--- a/記帳/申報/11508/11507-08_兩家分類帳.xlsx
+++ b/記帳/申報/11508/11507-08_兩家分類帳.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -525,118 +525,118 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1150831</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>銷項彙總</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>門市及B2B銷項(DU字軌)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>149128</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>7457</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>156585</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>11507-08期銷項合計(未稅151985/稅7600)扣除已個別入帳之天元2857/143;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>2857</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="D5" s="4" t="n">
+        <v>151985</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>7600</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>159585</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>【支出|銷貨成本】</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>1150710</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>DT67511402</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>永紳國際貿易</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>476</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>紅酒1瓶;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>1150716</t>
+          <t>1150710</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DM30331380</t>
+          <t>DT67511402</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>滙格股份有限公司</t>
+          <t>永紳國際貿易</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3810</v>
+        <v>476</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4001</v>
+        <v>500</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>果露糖漿5項;已申報11508期</t>
+          <t>紅酒1瓶;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>1150727</t>
+          <t>1150716</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DD05851388</t>
+          <t>DM30331380</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>德麥食品股份有限公司</t>
+          <t>滙格股份有限公司</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8938</v>
+        <v>3810</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>447</v>
+        <v>191</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9385</v>
+        <v>4001</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>烘焙原料13件(變裝黴/AOP發酵/鮮奶油/貝朵起酥片);已申報11508期</t>
+          <t>果露糖漿5項;已申報11508期</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>DD05851389</t>
+          <t>DD05851388</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -657,17 +657,17 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1629</v>
+        <v>8938</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1710</v>
+        <v>9385</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>貝朵可頌70g;已申報11508期</t>
+          <t>烘焙原料13件(變裝黴/AOP發酵/鮮奶油/貝朵起酥片);已申報11508期</t>
         </is>
       </c>
     </row>
@@ -679,57 +679,57 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>DM36903456</t>
+          <t>DD05851389</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>和司特股份有限公司</t>
+          <t>德麥食品股份有限公司</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4100</v>
+        <v>1629</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4305</v>
+        <v>1710</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>丹蔘萃取物+紅景天萃取物;已申報11508期</t>
+          <t>貝朵可頌70g;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>1150731</t>
+          <t>1150727</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CQ98634828</t>
+          <t>DM36903456</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>開元食品工業宜蘭營業所</t>
+          <t>和司特股份有限公司</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2563</v>
+        <v>4100</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2691</v>
+        <v>4305</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>戀職人鮮奶936ml×39;票面未印稅額依5%推算;已申報11508期</t>
+          <t>丹蔘萃取物+紅景天萃取物;已申報11508期</t>
         </is>
       </c>
     </row>
@@ -741,26 +741,26 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CQ98794568</t>
+          <t>CQ98634828</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>開元食品工業中北營業所</t>
+          <t>開元食品工業宜蘭營業所</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1971</v>
+        <v>2563</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2070</v>
+        <v>2691</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>戀職人鮮奶936ml×30;票面未印稅額依5%推算;已申報11508期</t>
+          <t>戀職人鮮奶936ml×39;票面未印稅額依5%推算;已申報11508期</t>
         </is>
       </c>
     </row>
@@ -772,119 +772,119 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>DG84731548</t>
+          <t>CQ98794568</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>億泰玻璃工業有限公司</t>
+          <t>開元食品工業中北營業所</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>31350</v>
+        <v>1971</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1568</v>
+        <v>99</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>32918</v>
+        <v>2070</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>瓶身印刷玻璃牙瓶2020支+鋁蓋墊片;現金付現折3%-970;買方統編72941298;已申報1</t>
+          <t>戀職人鮮奶936ml×30;票面未印稅額依5%推算;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>1150801</t>
+          <t>1150731</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CS57720952</t>
+          <t>DG84731548</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>全聯福利中心台中三民分公司</t>
+          <t>億泰玻璃工業有限公司</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>255</v>
+        <v>31350</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>1568</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>255</v>
+        <v>32918</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>瑞穗全脂鮮乳×3(免稅)</t>
+          <t>瓶身印刷玻璃牙瓶2020支+鋁蓋墊片;現金付現折3%-970;買方統編72941298;已申報1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>1150828</t>
+          <t>1150801</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>CA56707702</t>
+          <t>CS57720952</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>台灣瑰寶牛樟芝生物科技</t>
+          <t>全聯福利中心台中三民分公司</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8571</v>
+        <v>255</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9000</v>
+        <v>255</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>咖啡生豆;已申報11508期</t>
+          <t>瑞穗全脂鮮乳×3(免稅)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>1150831</t>
+          <t>1150828</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CQ98638116</t>
+          <t>CA56707702</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>開元食品工業股份有限公司宜蘭營業所</t>
+          <t>台灣瑰寶牛樟芝生物科技</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2826</v>
+        <v>8571</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>141</v>
+        <v>429</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2967</v>
+        <v>9000</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>戀職人鮮奶936ml×43;已申報11508期</t>
+          <t>咖啡生豆;已申報11508期</t>
         </is>
       </c>
     </row>
@@ -896,26 +896,26 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CQ98797385</t>
+          <t>CQ98638116</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>開元食品工業股份有限公司</t>
+          <t>開元食品工業股份有限公司宜蘭營業所</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1511</v>
+        <v>2826</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1587</v>
+        <v>2967</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>戀職人鮮奶936ml×23;已申報11508期</t>
+          <t>戀職人鮮奶936ml×43;已申報11508期</t>
         </is>
       </c>
     </row>
@@ -927,92 +927,92 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>CQ98797385</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>開元食品工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1511</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1587</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>戀職人鮮奶936ml×23;已申報11508期</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>1150831</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>CQ98797386</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>開元食品工業股份有限公司</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>開元起司絲;已申報11508期</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D21" s="4" t="n">
         <v>68271</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>3403</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <v>71674</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>【支出|租金】</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>1150707</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>DT07624903</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>蚨聚有限公司</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>21000</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>7月租金(時間到咖啡館);買方統編72941298;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>1150805</t>
+          <t>1150707</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>DT07624915</t>
+          <t>DT07624903</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1031,61 +1031,61 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>7月租金(時間到咖啡館);買方統編72941298;已申報11508期</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>1150805</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>DT07624915</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>蚨聚有限公司</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
           <t>8月租金(時間到咖啡館);買方統編72941298;已申報11508期</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D26" s="4" t="n">
         <v>40000</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E26" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F26" s="4" t="n">
         <v>42000</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>【支出|交際費】</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>1150709</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>CQ29579214</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>東森得易購</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>2857</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>漢來美食3000元好禮即享券</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CQ29579215</t>
+          <t>CQ29579214</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CQ29579216</t>
+          <t>CQ29579215</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CQ29579217</t>
+          <t>CQ29579216</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CQ29579218</t>
+          <t>CQ29579217</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CQ29579219</t>
+          <t>CQ29579218</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1245,56 +1245,56 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>1150709</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>CQ29579219</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>東森得易購</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>2857</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>漢來美食3000元好禮即享券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D35" s="4" t="n">
         <v>17142</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E35" s="4" t="n">
         <v>858</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F35" s="4" t="n">
         <v>18000</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>【支出|雜項費用】</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>1150703</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>DD40974257</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>連加網路商業股份有限公司</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>332</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>349</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>LINE Pay 6月交易手續費;金額與對方統編以PDF核實;買方統編72941298;已申報1</t>
         </is>
       </c>
     </row>
@@ -1306,26 +1306,26 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>DP39298640</t>
+          <t>DD40974257</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>新富町食堂</t>
+          <t>連加網路商業股份有限公司</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1740</v>
+        <v>332</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1827</v>
+        <v>349</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>餐費(桌號18)</t>
+          <t>LINE Pay 6月交易手續費;金額與對方統編以PDF核實;買方統編72941298;已申報1</t>
         </is>
       </c>
     </row>
@@ -1337,131 +1337,131 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>DT56020310</t>
+          <t>DP39298640</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>連加電子支付股份有限公司</t>
+          <t>新富町食堂</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>427</v>
+        <v>1740</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>448</v>
+        <v>1827</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>LINE Pay 6月交易手續費;金額與對方統編以PDF核實;買方統編72941298;已申報1</t>
+          <t>餐費(桌號18)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1150709</t>
+          <t>1150703</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CX36763733</t>
+          <t>DT56020310</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>7-ELEVEN成興店</t>
+          <t>連加電子支付股份有限公司</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>52</v>
+        <v>427</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>55</v>
+        <v>448</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>ibon列印+溫泉蛋;已申報11508期</t>
+          <t>LINE Pay 6月交易手續費;金額與對方統編以PDF核實;買方統編72941298;已申報1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>1150710</t>
+          <t>1150709</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CD57523585</t>
+          <t>CX36763733</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>沃克企業有限公司逢福營業所</t>
+          <t>7-ELEVEN成興店</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>停車費;票面無買方統編</t>
+          <t>ibon列印+溫泉蛋;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>1150718</t>
+          <t>1150710</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DG09230069</t>
+          <t>CD57523585</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>台灣國際開發事業</t>
+          <t>沃克企業有限公司逢福營業所</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>停車費(車號3672VU);已申報11508期</t>
+          <t>停車費;票面無買方統編</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>1150722</t>
+          <t>1150718</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DG09236287</t>
+          <t>DG09230069</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1470,48 +1470,48 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>停車費(車號CDE6379);已申報11508期</t>
+          <t>停車費(車號3672VU);已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>1150805</t>
+          <t>1150722</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>DD41088662</t>
+          <t>DG09236287</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>連加網路商業股份有限公司</t>
+          <t>台灣國際開發事業</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>199</v>
+        <v>100</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>LINE Pay 7月交易手續費;金額與對方統編以PDF核實;買方統編72941298;已申報1</t>
+          <t>停車費(車號CDE6379);已申報11508期</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>DT56075719</t>
+          <t>DD41088662</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>連加電子支付股份有限公司</t>
+          <t>連加網路商業股份有限公司</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>251</v>
+        <v>190</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1549,324 +1549,324 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>1150811</t>
+          <t>1150805</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>DQ45893585</t>
+          <t>DT56075719</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>(票面未載店名)</t>
+          <t>連加電子支付股份有限公司</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1979</v>
+        <v>251</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1979</v>
+        <v>264</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>甲殼素植物驅蟲噴霧+土壤防蟲粉(免稅)</t>
+          <t>LINE Pay 7月交易手續費;金額與對方統編以PDF核實;買方統編72941298;已申報1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1150815</t>
+          <t>1150811</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>DF13322559</t>
+          <t>DQ45893585</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>資廚管理顧問股份有限公司(iCHEF)</t>
+          <t>(票面未載店名)</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>11143</v>
+        <v>1979</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>557</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>11700</v>
+        <v>1979</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>iCHEF POS服務費;ezPay平台開立;買方抬頭鑫和洋行(信中未載統編數字);未稅稅額5%</t>
+          <t>甲殼素植物驅蟲噴霧+土壤防蟲粉(免稅)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
+          <t>1150815</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>DF13322559</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>資廚管理顧問股份有限公司(iCHEF)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>11143</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>557</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>11700</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>iCHEF POS服務費;ezPay平台開立;買方抬頭鑫和洋行(信中未載統編數字);未稅稅額5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>1150827</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>DG09246369</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>台灣國際開發事業</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>171</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>停車費(第二市場興中停車場;車號CDE6379);已申報11508期</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D50" s="4" t="n">
         <v>16573</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E50" s="4" t="n">
         <v>728</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F50" s="4" t="n">
         <v>17301</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>【支出|廣告行銷】</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>1150704</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>DD70999441</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>美商科高國際(Google)</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>1905</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Google Ads預付款;買方統編72941298;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1150806</t>
+          <t>1150704</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>DM14634071</t>
+          <t>DD70999441</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>藍格印刷國際企業有限公司</t>
+          <t>美商科高國際(Google)</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>933</v>
+        <v>1905</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>980</v>
+        <v>2000</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>5K摺式Menu+雙霧卡+運費;買方統編72941298;已申報11508期</t>
+          <t>Google Ads預付款;買方統編72941298;已申報11508期</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>1150806</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>DM14634071</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>藍格印刷國際企業有限公司</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>933</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>980</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>5K摺式Menu+雙霧卡+運費;買方統編72941298;已申報11508期</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
           <t>1150811</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>DM14636200</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>藍格印刷國際企業有限公司</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>796</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>836</v>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>5K摺式Menu+運費;買方統編72941298;已申報11508期</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D56" s="4" t="n">
         <v>3634</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E56" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F56" s="4" t="n">
         <v>3816</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>【支出|水電瓦斯】</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>1150710</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>帳單</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>中華電信</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>799</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F59" s="3" t="n">
         <v>799</v>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>115年6月電路統包專案月費繳費通知;非發票</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D60" s="4" t="n">
         <v>799</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F60" s="4" t="n">
         <v>799</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>【支出|運費】</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>1150713</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>收據</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>中華郵政</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>國內包裹特約記帳郵費單(綠界科技特約戶81g×1件)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1150729</t>
+          <t>1150713</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -1880,95 +1880,126 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>普通掛號函件執據郵資</t>
+          <t>國內包裹特約記帳郵費單(綠界科技特約戶81g×1件)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>1150729</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>收據</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>中華郵政</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>普通掛號函件執據郵資</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
           <t>1150731</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>CR62455519</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>新竹物流股份有限公司</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D65" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E65" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="F65" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>115年07-08月期運費;發票日115/7/31;買方統編72941298;已申報11508期</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D66" s="4" t="n">
         <v>260</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E66" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F66" s="4" t="n">
         <v>268</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>收入合計(含稅)</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>3000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>支出合計(含稅)</t>
+          <t>收入合計(含稅)</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>153858</v>
+        <v>159585</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>支出合計(含稅)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>153858</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
           <t>收支差(含稅)</t>
         </is>
       </c>
-      <c r="F69" s="4" t="n">
-        <v>-150858</v>
+      <c r="F70" s="4" t="n">
+        <v>5727</v>
       </c>
     </row>
   </sheetData>
@@ -1982,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2695,13 +2726,6 @@
         <v>58326</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>註:門市零售收入286,330(7月126,805/8月159,525)已含於銷貨收入</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
